--- a/boston_531.xlsx
+++ b/boston_531.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.001313</v>
+        <v>0.001494</v>
       </c>
       <c r="E2" t="n">
         <v>0.9991010299999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004118</v>
+        <v>0.004248</v>
       </c>
       <c r="G2" t="n">
         <v>0.892628772</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000162</v>
+        <v>0.000161</v>
       </c>
       <c r="I2" t="n">
         <v>2889.6</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.001211</v>
+        <v>0.001242</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003069</v>
+        <v>0.002341</v>
       </c>
       <c r="G3" t="n">
         <v>0.788635365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000264</v>
+        <v>0.000265</v>
       </c>
       <c r="I3" t="n">
         <v>2497.9</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.002912</v>
+        <v>0.002877</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004132</v>
+        <v>0.004869</v>
       </c>
       <c r="G4" t="n">
         <v>0.732018476</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000397</v>
+        <v>0.000403</v>
       </c>
       <c r="I4" t="n">
         <v>2283.7</v>

--- a/boston_531.xlsx
+++ b/boston_531.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.001494</v>
+        <v>0.001296</v>
       </c>
       <c r="E2" t="n">
         <v>0.9991010299999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004248</v>
+        <v>0.005355</v>
       </c>
       <c r="G2" t="n">
         <v>0.892628772</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000161</v>
+        <v>0.000153</v>
       </c>
       <c r="I2" t="n">
         <v>2889.6</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.001242</v>
+        <v>0.001182</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002341</v>
+        <v>0.002758</v>
       </c>
       <c r="G3" t="n">
         <v>0.788635365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000265</v>
+        <v>0.000262</v>
       </c>
       <c r="I3" t="n">
         <v>2497.9</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.002877</v>
+        <v>0.002851</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004869</v>
+        <v>0.005307</v>
       </c>
       <c r="G4" t="n">
         <v>0.732018476</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000403</v>
+        <v>0.000395</v>
       </c>
       <c r="I4" t="n">
         <v>2283.7</v>
